--- a/fhir/StructureDefinition-ehealth-servicerequest.xlsx
+++ b/fhir/StructureDefinition-ehealth-servicerequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2354" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2391" uniqueCount="528">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -365,7 +365,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -663,6 +663,22 @@
     <t>Used to mark that the action/service request may be performed as extra, meaning the action/service request may also be performed outside the resolved timing slots.</t>
   </si>
   <si>
+    <t>ServiceRequest.extension:aggregateId</t>
+  </si>
+  <si>
+    <t>aggregateId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-aggregate-id}
+</t>
+  </si>
+  <si>
+    <t>Aggregate identifier for grouping purposes.</t>
+  </si>
+  <si>
+    <t>An optional identifier used to associate this ServiceRequest with an aggregate or grouping context.</t>
+  </si>
+  <si>
     <t>ServiceRequest.modifierExtension</t>
   </si>
   <si>
@@ -764,7 +780,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|MedicationRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1|MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -790,7 +806,7 @@
 priorrenewed order</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -925,7 +941,7 @@
     <t>Classification of the requested service.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-category|4.0.1</t>
   </si>
   <si>
     <t>RF1-5</t>
@@ -1045,7 +1061,7 @@
     <t>Codified order entry details which are based on order context.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">prr-1
@@ -1109,7 +1125,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1179,7 +1195,7 @@
     <t>A coded concept identifying the pre-condition that should hold prior to performing a procedure.  For example "pain", "on flare-up", etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
   </si>
   <si>
     <t>boolean: precondition.negationInd (inversed - so negationInd = true means asNeeded=false CodeableConcept: precondition.observationEventCriterion[code="Assertion"].value</t>
@@ -1227,7 +1243,7 @@
 orderer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|RelatedPerson|Device)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1274,7 +1290,7 @@
     <t>Indicates specific responsibility of an individual within the care team, such as "Primary physician", "Team coordinator", "Caregiver", etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/participant-role</t>
+    <t>http://hl7.org/fhir/ValueSet/participant-role|4.0.1</t>
   </si>
   <si>
     <t>Request.performerType</t>
@@ -1339,7 +1355,7 @@
     <t>ServiceRequest.locationReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1364,7 +1380,7 @@
     <t>Diagnosis or problem codes justifying the reason for requesting the service investigation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1407,7 +1423,7 @@
     <t>ServiceRequest.insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Coverage|ClaimResponse)
+    <t xml:space="preserve">Reference(Coverage|4.0.1|ClaimResponse|4.0.1)
 </t>
   </si>
   <si>
@@ -1433,7 +1449,7 @@
 AOE</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1458,7 +1474,7 @@
     <t>ServiceRequest.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1499,7 +1515,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>targetSiteCode</t>
@@ -1542,7 +1558,7 @@
     <t>ServiceRequest.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -1949,7 +1965,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO63"/>
+  <dimension ref="A1:AO64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="41.6796875" customWidth="true" bestFit="true"/>
@@ -4567,43 +4583,41 @@
         <v>207</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>134</v>
+        <v>209</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N23" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="O23" t="s" s="2">
-        <v>212</v>
-      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
@@ -4651,7 +4665,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>213</v>
+        <v>139</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4660,7 +4674,7 @@
         <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>140</v>
@@ -4672,7 +4686,7 @@
         <v>79</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>79</v>
@@ -4683,14 +4697,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>79</v>
+        <v>213</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4703,24 +4717,26 @@
         <v>79</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="N24" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
       </c>
@@ -4768,7 +4784,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4780,30 +4796,30 @@
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>223</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4811,10 +4827,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>79</v>
@@ -4826,16 +4842,16 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4885,7 +4901,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4900,27 +4916,27 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>79</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4928,10 +4944,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>79</v>
@@ -4943,16 +4959,16 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>102</v>
+        <v>230</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5002,7 +5018,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -5017,13 +5033,13 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>79</v>
@@ -5041,14 +5057,14 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>238</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>79</v>
@@ -5060,15 +5076,17 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -5132,13 +5150,13 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>79</v>
@@ -5149,14 +5167,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5175,13 +5193,13 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5232,7 +5250,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -5247,13 +5265,13 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>79</v>
@@ -5264,21 +5282,21 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>79</v>
@@ -5290,20 +5308,16 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
       </c>
@@ -5351,13 +5365,13 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>79</v>
@@ -5366,13 +5380,13 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>79</v>
@@ -5383,18 +5397,18 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>79</v>
+        <v>259</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>88</v>
@@ -5403,24 +5417,26 @@
         <v>79</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>108</v>
+        <v>220</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="O30" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="M30" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
@@ -5444,13 +5460,13 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>266</v>
+        <v>79</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>267</v>
+        <v>79</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>268</v>
+        <v>79</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -5468,10 +5484,10 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>88</v>
@@ -5483,27 +5499,27 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>272</v>
+        <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>273</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5529,13 +5545,13 @@
         <v>108</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5561,13 +5577,13 @@
         <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
@@ -5585,7 +5601,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>88</v>
@@ -5600,27 +5616,27 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>131</v>
+        <v>275</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>79</v>
+        <v>278</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5628,35 +5644,33 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>284</v>
+        <v>108</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
       </c>
@@ -5680,13 +5694,13 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -5704,13 +5718,13 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
@@ -5719,16 +5733,16 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>292</v>
+        <v>131</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5736,10 +5750,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5750,7 +5764,7 @@
         <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>79</v>
@@ -5762,49 +5776,51 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>108</v>
+        <v>289</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="P33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="Y33" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="Z33" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q33" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="R33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>299</v>
-      </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
       </c>
@@ -5821,13 +5837,13 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>79</v>
@@ -5836,16 +5852,16 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>300</v>
+        <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -5853,10 +5869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5873,31 +5889,27 @@
         <v>79</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>305</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q34" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="R34" t="s" s="2">
         <v>79</v>
@@ -5918,13 +5930,13 @@
         <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>79</v>
+        <v>271</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>79</v>
+        <v>303</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>79</v>
+        <v>304</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>79</v>
@@ -5942,7 +5954,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5957,16 +5969,16 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>79</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -5974,14 +5986,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>314</v>
+        <v>79</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5994,28 +6006,32 @@
         <v>79</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q35" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O35" s="2"/>
-      <c r="P35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
         <v>79</v>
       </c>
@@ -6035,11 +6051,13 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>318</v>
+        <v>79</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
@@ -6057,7 +6075,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -6072,38 +6090,38 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>322</v>
+        <v>79</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>323</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>79</v>
@@ -6115,16 +6133,16 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6150,13 +6168,11 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -6174,53 +6190,53 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>331</v>
+        <v>79</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>79</v>
+        <v>324</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>79</v>
+        <v>327</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>79</v>
+        <v>330</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
@@ -6232,18 +6248,18 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>334</v>
+        <v>289</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>79</v>
       </c>
@@ -6267,13 +6283,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>79</v>
+        <v>294</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>79</v>
+        <v>334</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -6291,16 +6307,16 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>79</v>
+        <v>336</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>100</v>
@@ -6309,24 +6325,24 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6334,7 +6350,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
@@ -6349,16 +6365,18 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
       </c>
@@ -6406,10 +6424,10 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>88</v>
@@ -6421,35 +6439,35 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AL38" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AN38" t="s" s="2">
-        <v>346</v>
+        <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>347</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>349</v>
+        <v>79</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>88</v>
@@ -6464,13 +6482,13 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6521,10 +6539,10 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>88</v>
@@ -6536,31 +6554,31 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>147</v>
+        <v>350</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6579,13 +6597,13 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6636,7 +6654,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6651,31 +6669,31 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>364</v>
+        <v>147</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6694,13 +6712,13 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6727,13 +6745,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>371</v>
+        <v>79</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>372</v>
+        <v>79</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6751,7 +6769,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6766,31 +6784,31 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>79</v>
+        <v>367</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>79</v>
+        <v>368</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>376</v>
+        <v>79</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6809,13 +6827,13 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6842,13 +6860,13 @@
         <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>79</v>
+        <v>294</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>79</v>
+        <v>376</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>79</v>
+        <v>377</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>79</v>
@@ -6866,7 +6884,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6881,31 +6899,31 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>380</v>
+        <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>383</v>
+        <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6924,17 +6942,15 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -6983,7 +6999,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6998,31 +7014,31 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7041,16 +7057,16 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>284</v>
+        <v>392</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7076,13 +7092,13 @@
         <v>79</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>401</v>
+        <v>79</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>79</v>
@@ -7100,7 +7116,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -7115,38 +7131,38 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>79</v>
+        <v>400</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -7158,16 +7174,16 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>409</v>
+        <v>289</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7193,13 +7209,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>79</v>
+        <v>294</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>79</v>
+        <v>406</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>79</v>
+        <v>407</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7217,13 +7233,13 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
@@ -7232,16 +7248,16 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7249,14 +7265,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>79</v>
+        <v>413</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7275,15 +7291,17 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>284</v>
+        <v>414</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7308,13 +7326,13 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>419</v>
+        <v>79</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>420</v>
+        <v>79</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
@@ -7332,7 +7350,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7347,16 +7365,16 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>79</v>
+        <v>418</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>79</v>
+        <v>419</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7364,10 +7382,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7390,13 +7408,13 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7423,13 +7441,13 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>79</v>
+        <v>294</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>79</v>
+        <v>424</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
@@ -7447,7 +7465,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7468,10 +7486,10 @@
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
@@ -7479,10 +7497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7505,17 +7523,15 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>284</v>
+        <v>428</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N48" t="s" s="2">
         <v>429</v>
       </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7540,13 +7556,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>430</v>
+        <v>79</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>431</v>
+        <v>79</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7564,7 +7580,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7579,16 +7595,16 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>432</v>
+        <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>433</v>
+        <v>79</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7596,10 +7612,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7622,16 +7638,16 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>437</v>
+        <v>289</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7657,13 +7673,13 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>79</v>
+        <v>294</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>79</v>
+        <v>435</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>79</v>
+        <v>436</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7681,7 +7697,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7696,16 +7712,16 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7713,10 +7729,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7736,18 +7752,20 @@
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="L50" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7796,7 +7814,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7811,16 +7829,16 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="AN50" t="s" s="2">
-        <v>79</v>
+        <v>440</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7828,14 +7846,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>452</v>
+        <v>79</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7854,17 +7872,15 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -7913,7 +7929,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7928,13 +7944,13 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>79</v>
@@ -7945,14 +7961,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>79</v>
+        <v>457</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7968,19 +7984,19 @@
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8030,7 +8046,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -8045,13 +8061,13 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>79</v>
+        <v>462</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>79</v>
@@ -8062,14 +8078,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>468</v>
+        <v>79</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8088,20 +8104,18 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>284</v>
+        <v>466</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>472</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
       </c>
@@ -8125,13 +8139,13 @@
         <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>473</v>
+        <v>79</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>474</v>
+        <v>79</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -8149,7 +8163,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -8167,28 +8181,28 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>476</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>79</v>
+        <v>473</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8204,19 +8218,23 @@
         <v>79</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>478</v>
+        <v>289</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>48</v>
+        <v>474</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
       </c>
@@ -8240,13 +8258,13 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>79</v>
+        <v>294</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>79</v>
+        <v>478</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>79</v>
+        <v>479</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8264,7 +8282,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8279,27 +8297,27 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>482</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8310,7 +8328,7 @@
         <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
@@ -8322,13 +8340,13 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>150</v>
+        <v>483</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>152</v>
+        <v>484</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8379,53 +8397,53 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>153</v>
+        <v>482</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>79</v>
+        <v>485</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>79</v>
+        <v>337</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>154</v>
+        <v>486</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>79</v>
+        <v>487</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8437,17 +8455,15 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>485</v>
+        <v>151</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8484,31 +8500,31 @@
         <v>79</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>79</v>
@@ -8528,21 +8544,21 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>79</v>
+        <v>213</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8551,19 +8567,19 @@
         <v>79</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>488</v>
+        <v>134</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>491</v>
+        <v>216</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8601,38 +8617,40 @@
         <v>79</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AC57" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="AD57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>493</v>
+        <v>138</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>494</v>
+        <v>158</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>495</v>
+        <v>154</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>
@@ -8643,14 +8661,12 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>79</v>
       </c>
@@ -8671,16 +8687,16 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8718,19 +8734,17 @@
         <v>79</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>79</v>
+        <v>498</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8751,7 +8765,7 @@
         <v>131</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>79</v>
@@ -8762,13 +8776,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>79</v>
@@ -8790,16 +8804,16 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>150</v>
+        <v>503</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8849,7 +8863,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8870,7 +8884,7 @@
         <v>131</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>79</v>
@@ -8881,12 +8895,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="C60" s="2"/>
+        <v>492</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="D60" t="s" s="2">
         <v>79</v>
       </c>
@@ -8907,15 +8923,17 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>377</v>
+        <v>150</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -8964,7 +8982,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8985,7 +9003,7 @@
         <v>131</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>79</v>
@@ -9007,7 +9025,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>88</v>
@@ -9022,13 +9040,13 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9079,10 +9097,10 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>88</v>
@@ -9100,7 +9118,7 @@
         <v>131</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>79</v>
@@ -9111,10 +9129,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9122,7 +9140,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>88</v>
@@ -9137,7 +9155,7 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>150</v>
+        <v>512</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>513</v>
@@ -9194,10 +9212,10 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>88</v>
@@ -9212,10 +9230,10 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>332</v>
+        <v>131</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>79</v>
@@ -9226,10 +9244,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9240,7 +9258,7 @@
         <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>79</v>
@@ -9249,10 +9267,10 @@
         <v>79</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>517</v>
+        <v>150</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>518</v>
@@ -9260,9 +9278,7 @@
       <c r="M63" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="N63" t="s" s="2">
-        <v>520</v>
-      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -9311,13 +9327,13 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>79</v>
@@ -9326,18 +9342,135 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="B64" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="AM63" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO63" t="s" s="2">
+      <c r="AM64" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/fhir/StructureDefinition-ehealth-servicerequest.xlsx
+++ b/fhir/StructureDefinition-ehealth-servicerequest.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-servicerequest.xlsx
+++ b/fhir/StructureDefinition-ehealth-servicerequest.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-servicerequest.xlsx
+++ b/fhir/StructureDefinition-ehealth-servicerequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2391" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2428" uniqueCount="533">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -661,6 +661,22 @@
   </si>
   <si>
     <t>Used to mark that the action/service request may be performed as extra, meaning the action/service request may also be performed outside the resolved timing slots.</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:intendedQuestionnaireLinkage</t>
+  </si>
+  <si>
+    <t>intendedQuestionnaireLinkage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-intendedQuestionnaireLinkage}
+</t>
+  </si>
+  <si>
+    <t>QuestionnaireLinkage(s) intended for presenting the questionnaire responses of the action/service request</t>
+  </si>
+  <si>
+    <t>References the QuestionnaireLinkage(s) intended to be used when presenting the questionnaire responses of the action/service request, e.g. for cross-questionnaire or cross-version comparison. On PlanDefinition.action (any nesting level) it designates the linkages recommended by the plan template author; $apply copies it to the created ServiceRequest.</t>
   </si>
   <si>
     <t>ServiceRequest.extension:aggregateId</t>
@@ -1965,12 +1981,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO64"/>
+  <dimension ref="A1:AO65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.6796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.0390625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="30.62109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.69140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="25.0546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="37.7265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -4596,7 +4612,7 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>79</v>
@@ -4700,43 +4716,41 @@
         <v>212</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="D24" t="s" s="2">
-        <v>213</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>134</v>
+        <v>214</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N24" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="O24" t="s" s="2">
-        <v>217</v>
-      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
       </c>
@@ -4784,7 +4798,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>218</v>
+        <v>139</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4793,7 +4807,7 @@
         <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>140</v>
@@ -4805,7 +4819,7 @@
         <v>79</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>79</v>
@@ -4816,14 +4830,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4836,24 +4850,26 @@
         <v>79</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N25" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>79</v>
       </c>
@@ -4901,7 +4917,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4913,30 +4929,30 @@
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>224</v>
+        <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>225</v>
+        <v>79</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>226</v>
+        <v>131</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>227</v>
+        <v>79</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>228</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4944,10 +4960,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>79</v>
@@ -4959,16 +4975,16 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5018,7 +5034,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -5033,27 +5049,27 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>79</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5061,10 +5077,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>79</v>
@@ -5076,16 +5092,16 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>102</v>
+        <v>235</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5135,7 +5151,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -5150,13 +5166,13 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>79</v>
@@ -5174,14 +5190,14 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>243</v>
+        <v>79</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>79</v>
@@ -5193,15 +5209,17 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M28" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5265,13 +5283,13 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>79</v>
@@ -5282,14 +5300,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5308,13 +5326,13 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5365,7 +5383,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5380,13 +5398,13 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>79</v>
@@ -5397,21 +5415,21 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5423,20 +5441,16 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
@@ -5484,13 +5498,13 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
@@ -5499,13 +5513,13 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>79</v>
@@ -5516,18 +5530,18 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>88</v>
@@ -5536,24 +5550,26 @@
         <v>79</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>108</v>
+        <v>225</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="O31" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="M31" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>79</v>
       </c>
@@ -5577,13 +5593,13 @@
         <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>271</v>
+        <v>79</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>272</v>
+        <v>79</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>273</v>
+        <v>79</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
@@ -5601,10 +5617,10 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>88</v>
@@ -5616,27 +5632,27 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>277</v>
+        <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>278</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5662,13 +5678,13 @@
         <v>108</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5694,13 +5710,13 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -5718,7 +5734,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>88</v>
@@ -5733,27 +5749,27 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>131</v>
+        <v>280</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5761,35 +5777,33 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>289</v>
+        <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
       </c>
@@ -5813,13 +5827,13 @@
         <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
@@ -5837,13 +5851,13 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>79</v>
@@ -5852,16 +5866,16 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>297</v>
+        <v>131</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -5869,10 +5883,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5883,7 +5897,7 @@
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>79</v>
@@ -5895,49 +5909,51 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>108</v>
+        <v>294</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="P34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="Y34" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="Z34" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q34" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="R34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>79</v>
       </c>
@@ -5954,13 +5970,13 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
@@ -5969,16 +5985,16 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -5986,10 +6002,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6006,31 +6022,27 @@
         <v>79</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>310</v>
+        <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q35" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="R35" t="s" s="2">
         <v>79</v>
@@ -6051,13 +6063,13 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>79</v>
+        <v>276</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>79</v>
+        <v>308</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
@@ -6075,7 +6087,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -6090,16 +6102,16 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>79</v>
+        <v>313</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>79</v>
@@ -6107,14 +6119,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6127,28 +6139,32 @@
         <v>79</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="P36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q36" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="M36" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O36" s="2"/>
-      <c r="P36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
         <v>79</v>
       </c>
@@ -6168,11 +6184,13 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -6190,7 +6208,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -6205,38 +6223,38 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>325</v>
+        <v>79</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>327</v>
+        <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
@@ -6248,16 +6266,16 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6283,13 +6301,11 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -6307,53 +6323,53 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>336</v>
+        <v>79</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>79</v>
+        <v>329</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>79</v>
+        <v>332</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>79</v>
@@ -6365,18 +6381,18 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>339</v>
+        <v>294</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
       </c>
@@ -6400,13 +6416,13 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>79</v>
+        <v>339</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>79</v>
+        <v>340</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -6424,16 +6440,16 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>100</v>
@@ -6442,24 +6458,24 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>79</v>
+        <v>333</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6467,7 +6483,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>88</v>
@@ -6482,16 +6498,18 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
       </c>
@@ -6539,10 +6557,10 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>88</v>
@@ -6554,35 +6572,35 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AL39" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>350</v>
-      </c>
       <c r="AN39" t="s" s="2">
-        <v>351</v>
+        <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>352</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>354</v>
+        <v>79</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>88</v>
@@ -6597,13 +6615,13 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6654,10 +6672,10 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>88</v>
@@ -6669,31 +6687,31 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>147</v>
+        <v>355</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6712,13 +6730,13 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6769,7 +6787,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6784,31 +6802,31 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>369</v>
+        <v>147</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>79</v>
+        <v>368</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6827,13 +6845,13 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6860,13 +6878,13 @@
         <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>294</v>
+        <v>79</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>376</v>
+        <v>79</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>377</v>
+        <v>79</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>79</v>
@@ -6884,7 +6902,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6899,31 +6917,31 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>79</v>
+        <v>372</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>79</v>
+        <v>373</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>79</v>
+        <v>375</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6942,13 +6960,13 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6975,13 +6993,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -6999,7 +7017,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -7014,31 +7032,31 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>385</v>
+        <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>386</v>
+        <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>388</v>
+        <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7057,17 +7075,15 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7116,7 +7132,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -7131,31 +7147,31 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7174,16 +7190,16 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>289</v>
+        <v>397</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7209,13 +7225,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>294</v>
+        <v>79</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>406</v>
+        <v>79</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>407</v>
+        <v>79</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7233,7 +7249,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7248,38 +7264,38 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>79</v>
+        <v>405</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>79</v>
@@ -7291,16 +7307,16 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>414</v>
+        <v>294</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7326,13 +7342,13 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>79</v>
+        <v>412</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
@@ -7350,13 +7366,13 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
@@ -7365,16 +7381,16 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7382,14 +7398,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>79</v>
+        <v>418</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7408,15 +7424,17 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>289</v>
+        <v>419</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M47" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7441,13 +7459,13 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>294</v>
+        <v>79</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>424</v>
+        <v>79</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
@@ -7465,7 +7483,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7480,16 +7498,16 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>79</v>
+        <v>423</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>79</v>
+        <v>424</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
@@ -7497,10 +7515,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7523,13 +7541,13 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7556,13 +7574,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>79</v>
+        <v>429</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>79</v>
+        <v>430</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7580,7 +7598,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7601,10 +7619,10 @@
         <v>79</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7612,10 +7630,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7638,17 +7656,15 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>289</v>
+        <v>433</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N49" t="s" s="2">
         <v>434</v>
       </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7673,13 +7689,13 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>294</v>
+        <v>79</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>435</v>
+        <v>79</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>436</v>
+        <v>79</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7697,7 +7713,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7712,16 +7728,16 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>437</v>
+        <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>438</v>
+        <v>79</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7729,10 +7745,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7755,16 +7771,16 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>442</v>
+        <v>294</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7790,13 +7806,13 @@
         <v>79</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>79</v>
+        <v>440</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>79</v>
+        <v>441</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>79</v>
@@ -7814,7 +7830,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7829,16 +7845,16 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7846,10 +7862,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7869,18 +7885,20 @@
         <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="L51" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -7929,7 +7947,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7944,16 +7962,16 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AL51" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>455</v>
-      </c>
       <c r="AN51" t="s" s="2">
-        <v>79</v>
+        <v>445</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -7961,14 +7979,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>457</v>
+        <v>79</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7987,17 +8005,15 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8046,7 +8062,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -8061,13 +8077,13 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>79</v>
@@ -8078,14 +8094,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>79</v>
+        <v>462</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8101,19 +8117,19 @@
         <v>79</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8163,7 +8179,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -8178,13 +8194,13 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>79</v>
+        <v>467</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>79</v>
@@ -8195,14 +8211,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>473</v>
+        <v>79</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8221,20 +8237,18 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>289</v>
+        <v>471</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>477</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
       </c>
@@ -8258,13 +8272,13 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>294</v>
+        <v>79</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>478</v>
+        <v>79</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>479</v>
+        <v>79</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8282,7 +8296,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8300,28 +8314,28 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>481</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>79</v>
+        <v>478</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8337,19 +8351,23 @@
         <v>79</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>483</v>
+        <v>294</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>48</v>
+        <v>479</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>480</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8373,13 +8391,13 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>79</v>
+        <v>483</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>79</v>
+        <v>484</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8397,7 +8415,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8412,27 +8430,27 @@
         <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AL55" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>487</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8443,7 +8461,7 @@
         <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8455,13 +8473,13 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>150</v>
+        <v>488</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>152</v>
+        <v>489</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8512,53 +8530,53 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>153</v>
+        <v>487</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>79</v>
+        <v>490</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>79</v>
+        <v>342</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>154</v>
+        <v>491</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>79</v>
+        <v>492</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>213</v>
+        <v>79</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8570,17 +8588,15 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>490</v>
+        <v>151</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8617,31 +8633,31 @@
         <v>79</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
@@ -8661,21 +8677,21 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>79</v>
@@ -8684,19 +8700,19 @@
         <v>79</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>493</v>
+        <v>134</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>496</v>
+        <v>221</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8734,38 +8750,40 @@
         <v>79</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AC58" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="AD58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>498</v>
+        <v>138</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>499</v>
+        <v>158</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>500</v>
+        <v>154</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>79</v>
@@ -8776,14 +8794,12 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>502</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>79</v>
       </c>
@@ -8804,16 +8820,16 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8851,19 +8867,17 @@
         <v>79</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>79</v>
+        <v>503</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8884,7 +8898,7 @@
         <v>131</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>79</v>
@@ -8895,13 +8909,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>79</v>
@@ -8923,16 +8937,16 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>150</v>
+        <v>508</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8982,7 +8996,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -9003,7 +9017,7 @@
         <v>131</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>79</v>
@@ -9014,12 +9028,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>79</v>
       </c>
@@ -9040,15 +9056,17 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>382</v>
+        <v>150</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>500</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>501</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9097,7 +9115,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -9118,7 +9136,7 @@
         <v>131</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>79</v>
@@ -9140,7 +9158,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>88</v>
@@ -9155,13 +9173,13 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9212,10 +9230,10 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>88</v>
@@ -9233,7 +9251,7 @@
         <v>131</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>79</v>
@@ -9244,10 +9262,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9255,7 +9273,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>88</v>
@@ -9270,7 +9288,7 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>150</v>
+        <v>517</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>518</v>
@@ -9327,10 +9345,10 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>88</v>
@@ -9345,10 +9363,10 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>337</v>
+        <v>131</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>79</v>
@@ -9359,10 +9377,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9373,7 +9391,7 @@
         <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>79</v>
@@ -9382,10 +9400,10 @@
         <v>79</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>522</v>
+        <v>150</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>523</v>
@@ -9393,9 +9411,7 @@
       <c r="M64" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="N64" t="s" s="2">
-        <v>525</v>
-      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -9444,13 +9460,13 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>79</v>
@@ -9459,18 +9475,135 @@
         <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="B65" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="AM64" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO64" t="s" s="2">
+      <c r="AM65" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/fhir/StructureDefinition-ehealth-servicerequest.xlsx
+++ b/fhir/StructureDefinition-ehealth-servicerequest.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-servicerequest.xlsx
+++ b/fhir/StructureDefinition-ehealth-servicerequest.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-servicerequest.xlsx
+++ b/fhir/StructureDefinition-ehealth-servicerequest.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
